--- a/public/First_Questionnaire.xlsx
+++ b/public/First_Questionnaire.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Boggart-Project\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AF9B0ABD-0FE2-4271-9AAF-CE699B1A9E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9684AF0-F09C-4594-948C-6D5D75B5395F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{EA0FBA5E-5BA4-4ADF-9B36-49B2BB71C9D6}"/>
   </bookViews>
@@ -271,9 +271,6 @@
     <t>You will now see two scales describing an emotional experience</t>
   </si>
   <si>
-    <t>Please rate how you are feeling right now, with 0 being very negative and 10 being very positive.</t>
-  </si>
-  <si>
     <t>נא דרג/י כיצד את/ה מרגיש/ה כרגע, כאשר 1 מייצג מצב שלילי מאוד ו־9 מייצג מצב חיובי מאוד.</t>
   </si>
   <si>
@@ -290,9 +287,6 @@
   </si>
   <si>
     <t>Self-Assessment Manikin (SAM)</t>
-  </si>
-  <si>
-    <t>Please describe your arousal levels with 0 being calm and peaceful and 10 being emotional and aroused</t>
   </si>
   <si>
     <t>נא דרג/י את רמת העוררות שלך, כאשר 1 מייצג רוגע ושלווה ו־9 מייצג עוררות רגשית גבוהה.</t>
@@ -1093,6 +1087,12 @@
   </si>
   <si>
     <t>ההנאה מהחיים</t>
+  </si>
+  <si>
+    <t>Please rate how you are feeling right now, with 1 being very negative and 9 being very positive.</t>
+  </si>
+  <si>
+    <t>Please describe your arousal levels with 1 being calm and peaceful and 9 being emotional and aroused</t>
   </si>
 </sst>
 </file>
@@ -2878,13 +2878,13 @@
         <v>22</v>
       </c>
       <c r="F24" t="s">
+        <v>355</v>
+      </c>
+      <c r="G24" t="s">
         <v>83</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>84</v>
-      </c>
-      <c r="H24" t="s">
-        <v>85</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -2893,16 +2893,16 @@
         <v>9</v>
       </c>
       <c r="L24" t="s">
+        <v>85</v>
+      </c>
+      <c r="N24" t="s">
         <v>86</v>
       </c>
-      <c r="N24" t="s">
+      <c r="S24" t="s">
         <v>87</v>
       </c>
-      <c r="S24" t="s">
+      <c r="T24" t="s">
         <v>88</v>
-      </c>
-      <c r="T24" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -2916,13 +2916,13 @@
         <v>23</v>
       </c>
       <c r="F25" t="s">
+        <v>356</v>
+      </c>
+      <c r="G25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H25" t="s">
         <v>90</v>
-      </c>
-      <c r="G25" t="s">
-        <v>91</v>
-      </c>
-      <c r="H25" t="s">
-        <v>92</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -2931,13 +2931,13 @@
         <v>9</v>
       </c>
       <c r="L25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="T25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -2945,43 +2945,43 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E26">
         <v>24</v>
       </c>
       <c r="F26" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26" t="s">
         <v>97</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>5</v>
+      </c>
+      <c r="K26" t="s">
         <v>98</v>
       </c>
-      <c r="H26" t="s">
+      <c r="L26" t="s">
         <v>99</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>5</v>
-      </c>
-      <c r="K26" t="s">
+      <c r="M26" t="s">
         <v>100</v>
       </c>
-      <c r="L26" t="s">
+      <c r="N26" t="s">
         <v>101</v>
       </c>
-      <c r="M26" t="s">
+      <c r="T26" t="s">
         <v>102</v>
-      </c>
-      <c r="N26" t="s">
-        <v>103</v>
-      </c>
-      <c r="T26" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -2989,23 +2989,23 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E27">
         <v>25</v>
       </c>
       <c r="F27" t="s">
+        <v>103</v>
+      </c>
+      <c r="G27" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" t="s">
         <v>105</v>
       </c>
-      <c r="G27" t="s">
-        <v>106</v>
-      </c>
-      <c r="H27" t="s">
-        <v>107</v>
-      </c>
       <c r="I27">
         <v>0</v>
       </c>
@@ -3013,19 +3013,19 @@
         <v>5</v>
       </c>
       <c r="K27" t="s">
+        <v>98</v>
+      </c>
+      <c r="L27" t="s">
+        <v>99</v>
+      </c>
+      <c r="M27" t="s">
         <v>100</v>
       </c>
-      <c r="L27" t="s">
+      <c r="N27" t="s">
         <v>101</v>
       </c>
-      <c r="M27" t="s">
+      <c r="T27" t="s">
         <v>102</v>
-      </c>
-      <c r="N27" t="s">
-        <v>103</v>
-      </c>
-      <c r="T27" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3033,23 +3033,23 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E28">
         <v>26</v>
       </c>
       <c r="F28" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" t="s">
+        <v>107</v>
+      </c>
+      <c r="H28" t="s">
         <v>108</v>
       </c>
-      <c r="G28" t="s">
-        <v>109</v>
-      </c>
-      <c r="H28" t="s">
-        <v>110</v>
-      </c>
       <c r="I28">
         <v>0</v>
       </c>
@@ -3057,19 +3057,19 @@
         <v>5</v>
       </c>
       <c r="K28" t="s">
+        <v>98</v>
+      </c>
+      <c r="L28" t="s">
+        <v>99</v>
+      </c>
+      <c r="M28" t="s">
         <v>100</v>
       </c>
-      <c r="L28" t="s">
+      <c r="N28" t="s">
         <v>101</v>
       </c>
-      <c r="M28" t="s">
+      <c r="T28" t="s">
         <v>102</v>
-      </c>
-      <c r="N28" t="s">
-        <v>103</v>
-      </c>
-      <c r="T28" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3077,23 +3077,23 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E29">
         <v>27</v>
       </c>
       <c r="F29" t="s">
+        <v>109</v>
+      </c>
+      <c r="G29" t="s">
+        <v>110</v>
+      </c>
+      <c r="H29" t="s">
         <v>111</v>
       </c>
-      <c r="G29" t="s">
-        <v>112</v>
-      </c>
-      <c r="H29" t="s">
-        <v>113</v>
-      </c>
       <c r="I29">
         <v>0</v>
       </c>
@@ -3101,19 +3101,19 @@
         <v>5</v>
       </c>
       <c r="K29" t="s">
+        <v>98</v>
+      </c>
+      <c r="L29" t="s">
+        <v>99</v>
+      </c>
+      <c r="M29" t="s">
         <v>100</v>
       </c>
-      <c r="L29" t="s">
+      <c r="N29" t="s">
         <v>101</v>
       </c>
-      <c r="M29" t="s">
+      <c r="T29" t="s">
         <v>102</v>
-      </c>
-      <c r="N29" t="s">
-        <v>103</v>
-      </c>
-      <c r="T29" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3121,23 +3121,23 @@
         <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E30">
         <v>28</v>
       </c>
       <c r="F30" t="s">
+        <v>112</v>
+      </c>
+      <c r="G30" t="s">
+        <v>113</v>
+      </c>
+      <c r="H30" t="s">
         <v>114</v>
       </c>
-      <c r="G30" t="s">
-        <v>115</v>
-      </c>
-      <c r="H30" t="s">
-        <v>116</v>
-      </c>
       <c r="I30">
         <v>0</v>
       </c>
@@ -3145,19 +3145,19 @@
         <v>5</v>
       </c>
       <c r="K30" t="s">
+        <v>98</v>
+      </c>
+      <c r="L30" t="s">
+        <v>99</v>
+      </c>
+      <c r="M30" t="s">
         <v>100</v>
       </c>
-      <c r="L30" t="s">
+      <c r="N30" t="s">
         <v>101</v>
       </c>
-      <c r="M30" t="s">
+      <c r="T30" t="s">
         <v>102</v>
-      </c>
-      <c r="N30" t="s">
-        <v>103</v>
-      </c>
-      <c r="T30" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3165,43 +3165,43 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D31" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E31">
         <v>29</v>
       </c>
       <c r="F31" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" t="s">
+        <v>117</v>
+      </c>
+      <c r="H31" t="s">
         <v>118</v>
       </c>
-      <c r="G31" t="s">
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>5</v>
+      </c>
+      <c r="K31" t="s">
+        <v>98</v>
+      </c>
+      <c r="L31" t="s">
+        <v>99</v>
+      </c>
+      <c r="M31" t="s">
+        <v>100</v>
+      </c>
+      <c r="N31" t="s">
+        <v>101</v>
+      </c>
+      <c r="T31" t="s">
         <v>119</v>
-      </c>
-      <c r="H31" t="s">
-        <v>120</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>5</v>
-      </c>
-      <c r="K31" t="s">
-        <v>100</v>
-      </c>
-      <c r="L31" t="s">
-        <v>101</v>
-      </c>
-      <c r="M31" t="s">
-        <v>102</v>
-      </c>
-      <c r="N31" t="s">
-        <v>103</v>
-      </c>
-      <c r="T31" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -3209,23 +3209,23 @@
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E32">
         <v>30</v>
       </c>
       <c r="F32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" t="s">
+        <v>121</v>
+      </c>
+      <c r="H32" t="s">
         <v>122</v>
       </c>
-      <c r="G32" t="s">
-        <v>123</v>
-      </c>
-      <c r="H32" t="s">
-        <v>124</v>
-      </c>
       <c r="I32">
         <v>0</v>
       </c>
@@ -3233,19 +3233,19 @@
         <v>5</v>
       </c>
       <c r="K32" t="s">
+        <v>98</v>
+      </c>
+      <c r="L32" t="s">
+        <v>99</v>
+      </c>
+      <c r="M32" t="s">
         <v>100</v>
       </c>
-      <c r="L32" t="s">
+      <c r="N32" t="s">
         <v>101</v>
       </c>
-      <c r="M32" t="s">
-        <v>102</v>
-      </c>
-      <c r="N32" t="s">
-        <v>103</v>
-      </c>
       <c r="T32" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -3253,23 +3253,23 @@
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E33">
         <v>31</v>
       </c>
       <c r="F33" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" t="s">
+        <v>124</v>
+      </c>
+      <c r="H33" t="s">
         <v>125</v>
       </c>
-      <c r="G33" t="s">
-        <v>126</v>
-      </c>
-      <c r="H33" t="s">
-        <v>127</v>
-      </c>
       <c r="I33">
         <v>0</v>
       </c>
@@ -3277,19 +3277,19 @@
         <v>5</v>
       </c>
       <c r="K33" t="s">
+        <v>98</v>
+      </c>
+      <c r="L33" t="s">
+        <v>99</v>
+      </c>
+      <c r="M33" t="s">
         <v>100</v>
       </c>
-      <c r="L33" t="s">
+      <c r="N33" t="s">
         <v>101</v>
       </c>
-      <c r="M33" t="s">
-        <v>102</v>
-      </c>
-      <c r="N33" t="s">
-        <v>103</v>
-      </c>
       <c r="T33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -3297,23 +3297,23 @@
         <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E34">
         <v>32</v>
       </c>
       <c r="F34" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34" t="s">
         <v>128</v>
       </c>
-      <c r="G34" t="s">
-        <v>129</v>
-      </c>
-      <c r="H34" t="s">
-        <v>130</v>
-      </c>
       <c r="I34">
         <v>0</v>
       </c>
@@ -3321,19 +3321,19 @@
         <v>5</v>
       </c>
       <c r="K34" t="s">
+        <v>98</v>
+      </c>
+      <c r="L34" t="s">
+        <v>99</v>
+      </c>
+      <c r="M34" t="s">
         <v>100</v>
       </c>
-      <c r="L34" t="s">
+      <c r="N34" t="s">
         <v>101</v>
       </c>
-      <c r="M34" t="s">
-        <v>102</v>
-      </c>
-      <c r="N34" t="s">
-        <v>103</v>
-      </c>
       <c r="T34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -3341,23 +3341,23 @@
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E35">
         <v>33</v>
       </c>
       <c r="F35" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" t="s">
+        <v>130</v>
+      </c>
+      <c r="H35" t="s">
         <v>131</v>
       </c>
-      <c r="G35" t="s">
-        <v>132</v>
-      </c>
-      <c r="H35" t="s">
-        <v>133</v>
-      </c>
       <c r="I35">
         <v>0</v>
       </c>
@@ -3365,19 +3365,19 @@
         <v>5</v>
       </c>
       <c r="K35" t="s">
+        <v>98</v>
+      </c>
+      <c r="L35" t="s">
+        <v>99</v>
+      </c>
+      <c r="M35" t="s">
         <v>100</v>
       </c>
-      <c r="L35" t="s">
+      <c r="N35" t="s">
         <v>101</v>
       </c>
-      <c r="M35" t="s">
-        <v>102</v>
-      </c>
-      <c r="N35" t="s">
-        <v>103</v>
-      </c>
       <c r="T35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -3385,43 +3385,43 @@
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E36">
         <v>34</v>
       </c>
       <c r="F36" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36" t="s">
+        <v>133</v>
+      </c>
+      <c r="H36" t="s">
         <v>134</v>
       </c>
-      <c r="G36" t="s">
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>5</v>
+      </c>
+      <c r="K36" t="s">
+        <v>98</v>
+      </c>
+      <c r="L36" t="s">
+        <v>99</v>
+      </c>
+      <c r="M36" t="s">
+        <v>100</v>
+      </c>
+      <c r="N36" t="s">
+        <v>101</v>
+      </c>
+      <c r="T36" t="s">
         <v>135</v>
-      </c>
-      <c r="H36" t="s">
-        <v>136</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>5</v>
-      </c>
-      <c r="K36" t="s">
-        <v>100</v>
-      </c>
-      <c r="L36" t="s">
-        <v>101</v>
-      </c>
-      <c r="M36" t="s">
-        <v>102</v>
-      </c>
-      <c r="N36" t="s">
-        <v>103</v>
-      </c>
-      <c r="T36" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -3429,23 +3429,23 @@
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E37">
         <v>35</v>
       </c>
       <c r="F37" t="s">
+        <v>136</v>
+      </c>
+      <c r="G37" t="s">
+        <v>137</v>
+      </c>
+      <c r="H37" t="s">
         <v>138</v>
       </c>
-      <c r="G37" t="s">
-        <v>139</v>
-      </c>
-      <c r="H37" t="s">
-        <v>140</v>
-      </c>
       <c r="I37">
         <v>0</v>
       </c>
@@ -3453,19 +3453,19 @@
         <v>5</v>
       </c>
       <c r="K37" t="s">
+        <v>98</v>
+      </c>
+      <c r="L37" t="s">
+        <v>99</v>
+      </c>
+      <c r="M37" t="s">
         <v>100</v>
       </c>
-      <c r="L37" t="s">
+      <c r="N37" t="s">
         <v>101</v>
       </c>
-      <c r="M37" t="s">
-        <v>102</v>
-      </c>
-      <c r="N37" t="s">
-        <v>103</v>
-      </c>
       <c r="T37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -3473,23 +3473,23 @@
         <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E38">
         <v>36</v>
       </c>
       <c r="F38" t="s">
+        <v>139</v>
+      </c>
+      <c r="G38" t="s">
+        <v>140</v>
+      </c>
+      <c r="H38" t="s">
         <v>141</v>
       </c>
-      <c r="G38" t="s">
-        <v>142</v>
-      </c>
-      <c r="H38" t="s">
-        <v>143</v>
-      </c>
       <c r="I38">
         <v>0</v>
       </c>
@@ -3497,19 +3497,19 @@
         <v>5</v>
       </c>
       <c r="K38" t="s">
+        <v>98</v>
+      </c>
+      <c r="L38" t="s">
+        <v>99</v>
+      </c>
+      <c r="M38" t="s">
         <v>100</v>
       </c>
-      <c r="L38" t="s">
+      <c r="N38" t="s">
         <v>101</v>
       </c>
-      <c r="M38" t="s">
-        <v>102</v>
-      </c>
-      <c r="N38" t="s">
-        <v>103</v>
-      </c>
       <c r="T38" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -3517,23 +3517,23 @@
         <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D39" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E39">
         <v>37</v>
       </c>
       <c r="F39" t="s">
+        <v>142</v>
+      </c>
+      <c r="G39" t="s">
+        <v>143</v>
+      </c>
+      <c r="H39" t="s">
         <v>144</v>
       </c>
-      <c r="G39" t="s">
-        <v>145</v>
-      </c>
-      <c r="H39" t="s">
-        <v>146</v>
-      </c>
       <c r="I39">
         <v>0</v>
       </c>
@@ -3541,19 +3541,19 @@
         <v>5</v>
       </c>
       <c r="K39" t="s">
+        <v>98</v>
+      </c>
+      <c r="L39" t="s">
+        <v>99</v>
+      </c>
+      <c r="M39" t="s">
         <v>100</v>
       </c>
-      <c r="L39" t="s">
+      <c r="N39" t="s">
         <v>101</v>
       </c>
-      <c r="M39" t="s">
-        <v>102</v>
-      </c>
-      <c r="N39" t="s">
-        <v>103</v>
-      </c>
       <c r="T39" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -3561,23 +3561,23 @@
         <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E40">
         <v>38</v>
       </c>
       <c r="F40" t="s">
+        <v>145</v>
+      </c>
+      <c r="G40" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" t="s">
         <v>147</v>
       </c>
-      <c r="G40" t="s">
-        <v>148</v>
-      </c>
-      <c r="H40" t="s">
-        <v>149</v>
-      </c>
       <c r="I40">
         <v>0</v>
       </c>
@@ -3585,19 +3585,19 @@
         <v>5</v>
       </c>
       <c r="K40" t="s">
+        <v>98</v>
+      </c>
+      <c r="L40" t="s">
+        <v>99</v>
+      </c>
+      <c r="M40" t="s">
         <v>100</v>
       </c>
-      <c r="L40" t="s">
+      <c r="N40" t="s">
         <v>101</v>
       </c>
-      <c r="M40" t="s">
-        <v>102</v>
-      </c>
-      <c r="N40" t="s">
-        <v>103</v>
-      </c>
       <c r="T40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -3605,43 +3605,43 @@
         <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E41">
         <v>39</v>
       </c>
       <c r="F41" t="s">
+        <v>148</v>
+      </c>
+      <c r="G41" t="s">
+        <v>149</v>
+      </c>
+      <c r="H41" t="s">
         <v>150</v>
       </c>
-      <c r="G41" t="s">
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>5</v>
+      </c>
+      <c r="K41" t="s">
+        <v>98</v>
+      </c>
+      <c r="L41" t="s">
+        <v>99</v>
+      </c>
+      <c r="M41" t="s">
+        <v>100</v>
+      </c>
+      <c r="N41" t="s">
+        <v>101</v>
+      </c>
+      <c r="T41" t="s">
         <v>151</v>
-      </c>
-      <c r="H41" t="s">
-        <v>152</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>5</v>
-      </c>
-      <c r="K41" t="s">
-        <v>100</v>
-      </c>
-      <c r="L41" t="s">
-        <v>101</v>
-      </c>
-      <c r="M41" t="s">
-        <v>102</v>
-      </c>
-      <c r="N41" t="s">
-        <v>103</v>
-      </c>
-      <c r="T41" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -3649,23 +3649,23 @@
         <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E42">
         <v>40</v>
       </c>
       <c r="F42" t="s">
+        <v>152</v>
+      </c>
+      <c r="G42" t="s">
+        <v>153</v>
+      </c>
+      <c r="H42" t="s">
         <v>154</v>
       </c>
-      <c r="G42" t="s">
-        <v>155</v>
-      </c>
-      <c r="H42" t="s">
-        <v>156</v>
-      </c>
       <c r="I42">
         <v>0</v>
       </c>
@@ -3673,19 +3673,19 @@
         <v>5</v>
       </c>
       <c r="K42" t="s">
+        <v>98</v>
+      </c>
+      <c r="L42" t="s">
+        <v>99</v>
+      </c>
+      <c r="M42" t="s">
         <v>100</v>
       </c>
-      <c r="L42" t="s">
+      <c r="N42" t="s">
         <v>101</v>
       </c>
-      <c r="M42" t="s">
-        <v>102</v>
-      </c>
-      <c r="N42" t="s">
-        <v>103</v>
-      </c>
       <c r="T42" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -3693,23 +3693,23 @@
         <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E43">
         <v>41</v>
       </c>
       <c r="F43" t="s">
+        <v>155</v>
+      </c>
+      <c r="G43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H43" t="s">
         <v>157</v>
       </c>
-      <c r="G43" t="s">
-        <v>158</v>
-      </c>
-      <c r="H43" t="s">
-        <v>159</v>
-      </c>
       <c r="I43">
         <v>0</v>
       </c>
@@ -3717,19 +3717,19 @@
         <v>5</v>
       </c>
       <c r="K43" t="s">
+        <v>98</v>
+      </c>
+      <c r="L43" t="s">
+        <v>99</v>
+      </c>
+      <c r="M43" t="s">
         <v>100</v>
       </c>
-      <c r="L43" t="s">
+      <c r="N43" t="s">
         <v>101</v>
       </c>
-      <c r="M43" t="s">
-        <v>102</v>
-      </c>
-      <c r="N43" t="s">
-        <v>103</v>
-      </c>
       <c r="T43" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -3737,23 +3737,23 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E44">
         <v>42</v>
       </c>
       <c r="F44" t="s">
+        <v>158</v>
+      </c>
+      <c r="G44" t="s">
+        <v>159</v>
+      </c>
+      <c r="H44" t="s">
         <v>160</v>
       </c>
-      <c r="G44" t="s">
-        <v>161</v>
-      </c>
-      <c r="H44" t="s">
-        <v>162</v>
-      </c>
       <c r="I44">
         <v>0</v>
       </c>
@@ -3761,19 +3761,19 @@
         <v>5</v>
       </c>
       <c r="K44" t="s">
+        <v>98</v>
+      </c>
+      <c r="L44" t="s">
+        <v>99</v>
+      </c>
+      <c r="M44" t="s">
         <v>100</v>
       </c>
-      <c r="L44" t="s">
+      <c r="N44" t="s">
         <v>101</v>
       </c>
-      <c r="M44" t="s">
-        <v>102</v>
-      </c>
-      <c r="N44" t="s">
-        <v>103</v>
-      </c>
       <c r="T44" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -3781,23 +3781,23 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E45">
         <v>43</v>
       </c>
       <c r="F45" t="s">
+        <v>161</v>
+      </c>
+      <c r="G45" t="s">
+        <v>162</v>
+      </c>
+      <c r="H45" t="s">
         <v>163</v>
       </c>
-      <c r="G45" t="s">
-        <v>164</v>
-      </c>
-      <c r="H45" t="s">
-        <v>165</v>
-      </c>
       <c r="I45">
         <v>0</v>
       </c>
@@ -3805,19 +3805,19 @@
         <v>5</v>
       </c>
       <c r="K45" t="s">
+        <v>98</v>
+      </c>
+      <c r="L45" t="s">
+        <v>99</v>
+      </c>
+      <c r="M45" t="s">
         <v>100</v>
       </c>
-      <c r="L45" t="s">
+      <c r="N45" t="s">
         <v>101</v>
       </c>
-      <c r="M45" t="s">
-        <v>102</v>
-      </c>
-      <c r="N45" t="s">
-        <v>103</v>
-      </c>
       <c r="T45" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -3825,43 +3825,43 @@
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D46" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E46">
         <v>44</v>
       </c>
       <c r="F46" t="s">
+        <v>164</v>
+      </c>
+      <c r="G46" t="s">
+        <v>165</v>
+      </c>
+      <c r="H46" t="s">
         <v>166</v>
       </c>
-      <c r="G46" t="s">
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>5</v>
+      </c>
+      <c r="K46" t="s">
+        <v>98</v>
+      </c>
+      <c r="L46" t="s">
+        <v>99</v>
+      </c>
+      <c r="M46" t="s">
+        <v>100</v>
+      </c>
+      <c r="N46" t="s">
+        <v>101</v>
+      </c>
+      <c r="T46" t="s">
         <v>167</v>
-      </c>
-      <c r="H46" t="s">
-        <v>168</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>5</v>
-      </c>
-      <c r="K46" t="s">
-        <v>100</v>
-      </c>
-      <c r="L46" t="s">
-        <v>101</v>
-      </c>
-      <c r="M46" t="s">
-        <v>102</v>
-      </c>
-      <c r="N46" t="s">
-        <v>103</v>
-      </c>
-      <c r="T46" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -3869,23 +3869,23 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E47">
         <v>45</v>
       </c>
       <c r="F47" t="s">
+        <v>168</v>
+      </c>
+      <c r="G47" t="s">
+        <v>169</v>
+      </c>
+      <c r="H47" t="s">
         <v>170</v>
       </c>
-      <c r="G47" t="s">
-        <v>171</v>
-      </c>
-      <c r="H47" t="s">
-        <v>172</v>
-      </c>
       <c r="I47">
         <v>0</v>
       </c>
@@ -3893,19 +3893,19 @@
         <v>5</v>
       </c>
       <c r="K47" t="s">
+        <v>98</v>
+      </c>
+      <c r="L47" t="s">
+        <v>99</v>
+      </c>
+      <c r="M47" t="s">
         <v>100</v>
       </c>
-      <c r="L47" t="s">
+      <c r="N47" t="s">
         <v>101</v>
       </c>
-      <c r="M47" t="s">
-        <v>102</v>
-      </c>
-      <c r="N47" t="s">
-        <v>103</v>
-      </c>
       <c r="T47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -3913,23 +3913,23 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D48" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E48">
         <v>46</v>
       </c>
       <c r="F48" t="s">
+        <v>171</v>
+      </c>
+      <c r="G48" t="s">
+        <v>172</v>
+      </c>
+      <c r="H48" t="s">
         <v>173</v>
       </c>
-      <c r="G48" t="s">
-        <v>174</v>
-      </c>
-      <c r="H48" t="s">
-        <v>175</v>
-      </c>
       <c r="I48">
         <v>0</v>
       </c>
@@ -3937,19 +3937,19 @@
         <v>5</v>
       </c>
       <c r="K48" t="s">
+        <v>98</v>
+      </c>
+      <c r="L48" t="s">
+        <v>99</v>
+      </c>
+      <c r="M48" t="s">
         <v>100</v>
       </c>
-      <c r="L48" t="s">
+      <c r="N48" t="s">
         <v>101</v>
       </c>
-      <c r="M48" t="s">
-        <v>102</v>
-      </c>
-      <c r="N48" t="s">
-        <v>103</v>
-      </c>
       <c r="T48" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -3957,22 +3957,22 @@
         <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D49" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E49">
         <v>47</v>
       </c>
       <c r="F49" t="s">
+        <v>176</v>
+      </c>
+      <c r="G49" t="s">
+        <v>177</v>
+      </c>
+      <c r="H49" t="s">
         <v>178</v>
-      </c>
-      <c r="G49" t="s">
-        <v>179</v>
-      </c>
-      <c r="H49" t="s">
-        <v>180</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>10</v>
       </c>
       <c r="K49" t="s">
+        <v>98</v>
+      </c>
+      <c r="L49" t="s">
+        <v>99</v>
+      </c>
+      <c r="M49" t="s">
         <v>100</v>
       </c>
-      <c r="L49" t="s">
+      <c r="N49" t="s">
         <v>101</v>
       </c>
-      <c r="M49" t="s">
-        <v>102</v>
-      </c>
-      <c r="N49" t="s">
-        <v>103</v>
-      </c>
       <c r="T49" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -4001,22 +4001,22 @@
         <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D50" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E50">
         <v>48</v>
       </c>
       <c r="F50" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H50" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -4025,19 +4025,19 @@
         <v>10</v>
       </c>
       <c r="K50" t="s">
+        <v>98</v>
+      </c>
+      <c r="L50" t="s">
+        <v>99</v>
+      </c>
+      <c r="M50" t="s">
         <v>100</v>
       </c>
-      <c r="L50" t="s">
+      <c r="N50" t="s">
         <v>101</v>
       </c>
-      <c r="M50" t="s">
-        <v>102</v>
-      </c>
-      <c r="N50" t="s">
-        <v>103</v>
-      </c>
       <c r="T50" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -4045,19 +4045,19 @@
         <v>19</v>
       </c>
       <c r="C51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D51" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E51">
         <v>49</v>
       </c>
       <c r="F51" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G51" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H51" t="s">
         <v>75</v>
@@ -4069,13 +4069,13 @@
         <v>5</v>
       </c>
       <c r="O51" t="s">
+        <v>185</v>
+      </c>
+      <c r="P51" t="s">
+        <v>186</v>
+      </c>
+      <c r="T51" t="s">
         <v>187</v>
-      </c>
-      <c r="P51" t="s">
-        <v>188</v>
-      </c>
-      <c r="T51" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -4083,19 +4083,19 @@
         <v>19</v>
       </c>
       <c r="C52" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D52" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E52">
         <v>50</v>
       </c>
       <c r="F52" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G52" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H52" t="s">
         <v>75</v>
@@ -4107,13 +4107,13 @@
         <v>5</v>
       </c>
       <c r="O52" t="s">
+        <v>185</v>
+      </c>
+      <c r="P52" t="s">
+        <v>186</v>
+      </c>
+      <c r="T52" t="s">
         <v>187</v>
-      </c>
-      <c r="P52" t="s">
-        <v>188</v>
-      </c>
-      <c r="T52" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -4121,19 +4121,19 @@
         <v>19</v>
       </c>
       <c r="C53" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D53" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E53">
         <v>51</v>
       </c>
       <c r="F53" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G53" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H53" t="s">
         <v>75</v>
@@ -4145,13 +4145,13 @@
         <v>5</v>
       </c>
       <c r="O53" t="s">
+        <v>185</v>
+      </c>
+      <c r="P53" t="s">
+        <v>186</v>
+      </c>
+      <c r="T53" t="s">
         <v>187</v>
-      </c>
-      <c r="P53" t="s">
-        <v>188</v>
-      </c>
-      <c r="T53" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -4159,19 +4159,19 @@
         <v>20</v>
       </c>
       <c r="C54" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D54" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E54">
         <v>52</v>
       </c>
       <c r="F54" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G54" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H54" t="s">
         <v>75</v>
@@ -4183,13 +4183,13 @@
         <v>5</v>
       </c>
       <c r="O54" t="s">
+        <v>185</v>
+      </c>
+      <c r="P54" t="s">
+        <v>186</v>
+      </c>
+      <c r="T54" t="s">
         <v>187</v>
-      </c>
-      <c r="P54" t="s">
-        <v>188</v>
-      </c>
-      <c r="T54" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -4197,19 +4197,19 @@
         <v>20</v>
       </c>
       <c r="C55" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D55" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E55">
         <v>53</v>
       </c>
       <c r="F55" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G55" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H55" t="s">
         <v>75</v>
@@ -4221,13 +4221,13 @@
         <v>5</v>
       </c>
       <c r="O55" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P55" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T55" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -4235,19 +4235,19 @@
         <v>20</v>
       </c>
       <c r="C56" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D56" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E56">
         <v>54</v>
       </c>
       <c r="F56" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G56" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H56" t="s">
         <v>75</v>
@@ -4259,13 +4259,13 @@
         <v>5</v>
       </c>
       <c r="O56" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P56" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T56" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -4273,19 +4273,19 @@
         <v>21</v>
       </c>
       <c r="C57" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D57" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E57">
         <v>55</v>
       </c>
       <c r="F57" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G57" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H57" t="s">
         <v>75</v>
@@ -4297,13 +4297,13 @@
         <v>5</v>
       </c>
       <c r="O57" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T57" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -4311,19 +4311,19 @@
         <v>21</v>
       </c>
       <c r="C58" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D58" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E58">
         <v>56</v>
       </c>
       <c r="F58" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G58" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H58" t="s">
         <v>75</v>
@@ -4335,13 +4335,13 @@
         <v>5</v>
       </c>
       <c r="O58" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P58" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T58" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -4349,19 +4349,19 @@
         <v>21</v>
       </c>
       <c r="C59" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D59" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E59">
         <v>57</v>
       </c>
       <c r="F59" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G59" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H59" t="s">
         <v>75</v>
@@ -4373,13 +4373,13 @@
         <v>5</v>
       </c>
       <c r="O59" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P59" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T59" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -4387,19 +4387,19 @@
         <v>22</v>
       </c>
       <c r="C60" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D60" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E60">
         <v>58</v>
       </c>
       <c r="F60" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G60" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H60" t="s">
         <v>75</v>
@@ -4411,13 +4411,13 @@
         <v>5</v>
       </c>
       <c r="O60" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P60" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T60" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -4425,19 +4425,19 @@
         <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D61" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E61">
         <v>59</v>
       </c>
       <c r="F61" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G61" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H61" t="s">
         <v>75</v>
@@ -4449,13 +4449,13 @@
         <v>5</v>
       </c>
       <c r="O61" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P61" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T61" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -4463,19 +4463,19 @@
         <v>22</v>
       </c>
       <c r="C62" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D62" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E62">
         <v>60</v>
       </c>
       <c r="F62" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G62" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H62" t="s">
         <v>75</v>
@@ -4487,13 +4487,13 @@
         <v>5</v>
       </c>
       <c r="O62" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P62" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T62" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -4501,19 +4501,19 @@
         <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D63" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E63">
         <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G63" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H63" t="s">
         <v>75</v>
@@ -4525,13 +4525,13 @@
         <v>5</v>
       </c>
       <c r="O63" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P63" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T63" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -4539,43 +4539,43 @@
         <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D64" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E64">
         <v>62</v>
       </c>
       <c r="F64" t="s">
+        <v>216</v>
+      </c>
+      <c r="G64" t="s">
+        <v>217</v>
+      </c>
+      <c r="H64" t="s">
+        <v>178</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>5</v>
+      </c>
+      <c r="K64" t="s">
         <v>218</v>
       </c>
-      <c r="G64" t="s">
+      <c r="L64" t="s">
         <v>219</v>
       </c>
-      <c r="H64" t="s">
-        <v>180</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>5</v>
-      </c>
-      <c r="K64" t="s">
+      <c r="M64" t="s">
         <v>220</v>
       </c>
-      <c r="L64" t="s">
+      <c r="N64" t="s">
         <v>221</v>
       </c>
-      <c r="M64" t="s">
+      <c r="T64" t="s">
         <v>222</v>
-      </c>
-      <c r="N64" t="s">
-        <v>223</v>
-      </c>
-      <c r="T64" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -4583,22 +4583,22 @@
         <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D65" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E65">
         <v>63</v>
       </c>
       <c r="F65" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G65" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H65" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -4607,19 +4607,19 @@
         <v>5</v>
       </c>
       <c r="K65" t="s">
+        <v>218</v>
+      </c>
+      <c r="L65" t="s">
+        <v>219</v>
+      </c>
+      <c r="M65" t="s">
         <v>220</v>
       </c>
-      <c r="L65" t="s">
+      <c r="N65" t="s">
         <v>221</v>
       </c>
-      <c r="M65" t="s">
+      <c r="T65" t="s">
         <v>222</v>
-      </c>
-      <c r="N65" t="s">
-        <v>223</v>
-      </c>
-      <c r="T65" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -4627,22 +4627,22 @@
         <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D66" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E66">
         <v>64</v>
       </c>
       <c r="F66" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G66" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H66" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -4651,19 +4651,19 @@
         <v>5</v>
       </c>
       <c r="K66" t="s">
+        <v>218</v>
+      </c>
+      <c r="L66" t="s">
+        <v>219</v>
+      </c>
+      <c r="M66" t="s">
         <v>220</v>
       </c>
-      <c r="L66" t="s">
+      <c r="N66" t="s">
         <v>221</v>
       </c>
-      <c r="M66" t="s">
+      <c r="T66" t="s">
         <v>222</v>
-      </c>
-      <c r="N66" t="s">
-        <v>223</v>
-      </c>
-      <c r="T66" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -4671,22 +4671,22 @@
         <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D67" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E67">
         <v>65</v>
       </c>
       <c r="F67" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G67" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H67" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -4695,19 +4695,19 @@
         <v>5</v>
       </c>
       <c r="K67" t="s">
+        <v>218</v>
+      </c>
+      <c r="L67" t="s">
+        <v>219</v>
+      </c>
+      <c r="M67" t="s">
         <v>220</v>
       </c>
-      <c r="L67" t="s">
+      <c r="N67" t="s">
         <v>221</v>
       </c>
-      <c r="M67" t="s">
+      <c r="T67" t="s">
         <v>222</v>
-      </c>
-      <c r="N67" t="s">
-        <v>223</v>
-      </c>
-      <c r="T67" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -4715,22 +4715,22 @@
         <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D68" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E68">
         <v>66</v>
       </c>
       <c r="F68" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G68" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H68" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -4739,19 +4739,19 @@
         <v>5</v>
       </c>
       <c r="K68" t="s">
+        <v>218</v>
+      </c>
+      <c r="L68" t="s">
+        <v>219</v>
+      </c>
+      <c r="M68" t="s">
         <v>220</v>
       </c>
-      <c r="L68" t="s">
+      <c r="N68" t="s">
         <v>221</v>
       </c>
-      <c r="M68" t="s">
+      <c r="T68" t="s">
         <v>222</v>
-      </c>
-      <c r="N68" t="s">
-        <v>223</v>
-      </c>
-      <c r="T68" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -4759,22 +4759,22 @@
         <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D69" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E69">
         <v>67</v>
       </c>
       <c r="F69" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G69" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H69" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -4783,19 +4783,19 @@
         <v>5</v>
       </c>
       <c r="K69" t="s">
+        <v>218</v>
+      </c>
+      <c r="L69" t="s">
+        <v>219</v>
+      </c>
+      <c r="M69" t="s">
         <v>220</v>
       </c>
-      <c r="L69" t="s">
+      <c r="N69" t="s">
         <v>221</v>
       </c>
-      <c r="M69" t="s">
+      <c r="T69" t="s">
         <v>222</v>
-      </c>
-      <c r="N69" t="s">
-        <v>223</v>
-      </c>
-      <c r="T69" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -4803,22 +4803,22 @@
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D70" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E70">
         <v>68</v>
       </c>
       <c r="F70" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G70" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H70" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4827,19 +4827,19 @@
         <v>5</v>
       </c>
       <c r="K70" t="s">
+        <v>218</v>
+      </c>
+      <c r="L70" t="s">
+        <v>219</v>
+      </c>
+      <c r="M70" t="s">
         <v>220</v>
       </c>
-      <c r="L70" t="s">
+      <c r="N70" t="s">
         <v>221</v>
       </c>
-      <c r="M70" t="s">
+      <c r="T70" t="s">
         <v>222</v>
-      </c>
-      <c r="N70" t="s">
-        <v>223</v>
-      </c>
-      <c r="T70" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -4847,22 +4847,22 @@
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D71" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E71">
         <v>69</v>
       </c>
       <c r="F71" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G71" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H71" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -4871,19 +4871,19 @@
         <v>5</v>
       </c>
       <c r="K71" t="s">
+        <v>218</v>
+      </c>
+      <c r="L71" t="s">
+        <v>219</v>
+      </c>
+      <c r="M71" t="s">
         <v>220</v>
       </c>
-      <c r="L71" t="s">
+      <c r="N71" t="s">
         <v>221</v>
       </c>
-      <c r="M71" t="s">
+      <c r="T71" t="s">
         <v>222</v>
-      </c>
-      <c r="N71" t="s">
-        <v>223</v>
-      </c>
-      <c r="T71" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -4891,22 +4891,22 @@
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D72" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E72">
         <v>70</v>
       </c>
       <c r="F72" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G72" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H72" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -4915,19 +4915,19 @@
         <v>5</v>
       </c>
       <c r="K72" t="s">
+        <v>218</v>
+      </c>
+      <c r="L72" t="s">
+        <v>219</v>
+      </c>
+      <c r="M72" t="s">
         <v>220</v>
       </c>
-      <c r="L72" t="s">
+      <c r="N72" t="s">
         <v>221</v>
       </c>
-      <c r="M72" t="s">
+      <c r="T72" t="s">
         <v>222</v>
-      </c>
-      <c r="N72" t="s">
-        <v>223</v>
-      </c>
-      <c r="T72" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -4935,22 +4935,22 @@
         <v>27</v>
       </c>
       <c r="C73" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D73" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E73">
         <v>71</v>
       </c>
       <c r="F73" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G73" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H73" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -4959,19 +4959,19 @@
         <v>5</v>
       </c>
       <c r="K73" t="s">
+        <v>218</v>
+      </c>
+      <c r="L73" t="s">
+        <v>219</v>
+      </c>
+      <c r="M73" t="s">
         <v>220</v>
       </c>
-      <c r="L73" t="s">
+      <c r="N73" t="s">
         <v>221</v>
       </c>
-      <c r="M73" t="s">
+      <c r="T73" t="s">
         <v>222</v>
-      </c>
-      <c r="N73" t="s">
-        <v>223</v>
-      </c>
-      <c r="T73" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -4979,22 +4979,22 @@
         <v>27</v>
       </c>
       <c r="C74" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D74" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E74">
         <v>72</v>
       </c>
       <c r="F74" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G74" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H74" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -5003,19 +5003,19 @@
         <v>5</v>
       </c>
       <c r="K74" t="s">
+        <v>218</v>
+      </c>
+      <c r="L74" t="s">
+        <v>219</v>
+      </c>
+      <c r="M74" t="s">
         <v>220</v>
       </c>
-      <c r="L74" t="s">
+      <c r="N74" t="s">
         <v>221</v>
       </c>
-      <c r="M74" t="s">
+      <c r="T74" t="s">
         <v>222</v>
-      </c>
-      <c r="N74" t="s">
-        <v>223</v>
-      </c>
-      <c r="T74" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -5023,22 +5023,22 @@
         <v>27</v>
       </c>
       <c r="C75" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D75" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E75">
         <v>73</v>
       </c>
       <c r="F75" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G75" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H75" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -5047,19 +5047,19 @@
         <v>5</v>
       </c>
       <c r="K75" t="s">
+        <v>218</v>
+      </c>
+      <c r="L75" t="s">
+        <v>219</v>
+      </c>
+      <c r="M75" t="s">
         <v>220</v>
       </c>
-      <c r="L75" t="s">
+      <c r="N75" t="s">
         <v>221</v>
       </c>
-      <c r="M75" t="s">
+      <c r="T75" t="s">
         <v>222</v>
-      </c>
-      <c r="N75" t="s">
-        <v>223</v>
-      </c>
-      <c r="T75" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -5067,22 +5067,22 @@
         <v>28</v>
       </c>
       <c r="C76" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D76" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E76">
         <v>74</v>
       </c>
       <c r="F76" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G76" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H76" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -5091,19 +5091,19 @@
         <v>5</v>
       </c>
       <c r="K76" t="s">
+        <v>218</v>
+      </c>
+      <c r="L76" t="s">
+        <v>219</v>
+      </c>
+      <c r="M76" t="s">
         <v>220</v>
       </c>
-      <c r="L76" t="s">
+      <c r="N76" t="s">
         <v>221</v>
       </c>
-      <c r="M76" t="s">
+      <c r="T76" t="s">
         <v>222</v>
-      </c>
-      <c r="N76" t="s">
-        <v>223</v>
-      </c>
-      <c r="T76" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -5111,22 +5111,22 @@
         <v>28</v>
       </c>
       <c r="C77" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D77" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E77">
         <v>75</v>
       </c>
       <c r="F77" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G77" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H77" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -5135,19 +5135,19 @@
         <v>5</v>
       </c>
       <c r="K77" t="s">
+        <v>218</v>
+      </c>
+      <c r="L77" t="s">
+        <v>219</v>
+      </c>
+      <c r="M77" t="s">
         <v>220</v>
       </c>
-      <c r="L77" t="s">
+      <c r="N77" t="s">
         <v>221</v>
       </c>
-      <c r="M77" t="s">
+      <c r="T77" t="s">
         <v>222</v>
-      </c>
-      <c r="N77" t="s">
-        <v>223</v>
-      </c>
-      <c r="T77" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -5155,22 +5155,22 @@
         <v>28</v>
       </c>
       <c r="C78" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D78" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E78">
         <v>76</v>
       </c>
       <c r="F78" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G78" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H78" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -5179,19 +5179,19 @@
         <v>5</v>
       </c>
       <c r="K78" t="s">
+        <v>218</v>
+      </c>
+      <c r="L78" t="s">
+        <v>219</v>
+      </c>
+      <c r="M78" t="s">
         <v>220</v>
       </c>
-      <c r="L78" t="s">
+      <c r="N78" t="s">
         <v>221</v>
       </c>
-      <c r="M78" t="s">
+      <c r="T78" t="s">
         <v>222</v>
-      </c>
-      <c r="N78" t="s">
-        <v>223</v>
-      </c>
-      <c r="T78" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -5199,22 +5199,22 @@
         <v>29</v>
       </c>
       <c r="C79" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D79" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E79">
         <v>77</v>
       </c>
       <c r="F79" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G79" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H79" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -5223,19 +5223,19 @@
         <v>5</v>
       </c>
       <c r="K79" t="s">
+        <v>218</v>
+      </c>
+      <c r="L79" t="s">
+        <v>219</v>
+      </c>
+      <c r="M79" t="s">
         <v>220</v>
       </c>
-      <c r="L79" t="s">
+      <c r="N79" t="s">
         <v>221</v>
       </c>
-      <c r="M79" t="s">
+      <c r="T79" t="s">
         <v>222</v>
-      </c>
-      <c r="N79" t="s">
-        <v>223</v>
-      </c>
-      <c r="T79" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -5243,22 +5243,22 @@
         <v>29</v>
       </c>
       <c r="C80" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D80" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E80">
         <v>78</v>
       </c>
       <c r="F80" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G80" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H80" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -5267,19 +5267,19 @@
         <v>5</v>
       </c>
       <c r="K80" t="s">
+        <v>218</v>
+      </c>
+      <c r="L80" t="s">
+        <v>219</v>
+      </c>
+      <c r="M80" t="s">
         <v>220</v>
       </c>
-      <c r="L80" t="s">
+      <c r="N80" t="s">
         <v>221</v>
       </c>
-      <c r="M80" t="s">
+      <c r="T80" t="s">
         <v>222</v>
-      </c>
-      <c r="N80" t="s">
-        <v>223</v>
-      </c>
-      <c r="T80" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
@@ -5287,22 +5287,22 @@
         <v>29</v>
       </c>
       <c r="C81" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D81" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E81">
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G81" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H81" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -5311,19 +5311,19 @@
         <v>5</v>
       </c>
       <c r="K81" t="s">
+        <v>218</v>
+      </c>
+      <c r="L81" t="s">
+        <v>219</v>
+      </c>
+      <c r="M81" t="s">
         <v>220</v>
       </c>
-      <c r="L81" t="s">
+      <c r="N81" t="s">
         <v>221</v>
       </c>
-      <c r="M81" t="s">
+      <c r="T81" t="s">
         <v>222</v>
-      </c>
-      <c r="N81" t="s">
-        <v>223</v>
-      </c>
-      <c r="T81" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
@@ -5331,22 +5331,22 @@
         <v>30</v>
       </c>
       <c r="C82" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D82" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E82">
         <v>80</v>
       </c>
       <c r="F82" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G82" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H82" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -5355,19 +5355,19 @@
         <v>5</v>
       </c>
       <c r="K82" t="s">
+        <v>218</v>
+      </c>
+      <c r="L82" t="s">
+        <v>219</v>
+      </c>
+      <c r="M82" t="s">
         <v>220</v>
       </c>
-      <c r="L82" t="s">
+      <c r="N82" t="s">
         <v>221</v>
       </c>
-      <c r="M82" t="s">
+      <c r="T82" t="s">
         <v>222</v>
-      </c>
-      <c r="N82" t="s">
-        <v>223</v>
-      </c>
-      <c r="T82" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
@@ -5375,22 +5375,22 @@
         <v>30</v>
       </c>
       <c r="C83" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D83" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E83">
         <v>81</v>
       </c>
       <c r="F83" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G83" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H83" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -5399,19 +5399,19 @@
         <v>5</v>
       </c>
       <c r="K83" t="s">
+        <v>218</v>
+      </c>
+      <c r="L83" t="s">
+        <v>219</v>
+      </c>
+      <c r="M83" t="s">
         <v>220</v>
       </c>
-      <c r="L83" t="s">
+      <c r="N83" t="s">
         <v>221</v>
       </c>
-      <c r="M83" t="s">
+      <c r="T83" t="s">
         <v>222</v>
-      </c>
-      <c r="N83" t="s">
-        <v>223</v>
-      </c>
-      <c r="T83" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -5419,22 +5419,22 @@
         <v>30</v>
       </c>
       <c r="C84" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D84" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E84">
         <v>82</v>
       </c>
       <c r="F84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G84" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H84" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -5443,19 +5443,19 @@
         <v>5</v>
       </c>
       <c r="K84" t="s">
+        <v>218</v>
+      </c>
+      <c r="L84" t="s">
+        <v>219</v>
+      </c>
+      <c r="M84" t="s">
         <v>220</v>
       </c>
-      <c r="L84" t="s">
+      <c r="N84" t="s">
         <v>221</v>
       </c>
-      <c r="M84" t="s">
+      <c r="T84" t="s">
         <v>222</v>
-      </c>
-      <c r="N84" t="s">
-        <v>223</v>
-      </c>
-      <c r="T84" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
@@ -5463,22 +5463,22 @@
         <v>31</v>
       </c>
       <c r="C85" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D85" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E85">
         <v>83</v>
       </c>
       <c r="F85" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G85" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H85" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -5487,19 +5487,19 @@
         <v>5</v>
       </c>
       <c r="K85" t="s">
+        <v>218</v>
+      </c>
+      <c r="L85" t="s">
+        <v>219</v>
+      </c>
+      <c r="M85" t="s">
         <v>220</v>
       </c>
-      <c r="L85" t="s">
+      <c r="N85" t="s">
         <v>221</v>
       </c>
-      <c r="M85" t="s">
+      <c r="T85" t="s">
         <v>222</v>
-      </c>
-      <c r="N85" t="s">
-        <v>223</v>
-      </c>
-      <c r="T85" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
@@ -5507,22 +5507,22 @@
         <v>31</v>
       </c>
       <c r="C86" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D86" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E86">
         <v>84</v>
       </c>
       <c r="F86" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G86" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H86" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -5531,19 +5531,19 @@
         <v>5</v>
       </c>
       <c r="K86" t="s">
+        <v>218</v>
+      </c>
+      <c r="L86" t="s">
+        <v>219</v>
+      </c>
+      <c r="M86" t="s">
         <v>220</v>
       </c>
-      <c r="L86" t="s">
+      <c r="N86" t="s">
         <v>221</v>
       </c>
-      <c r="M86" t="s">
+      <c r="T86" t="s">
         <v>222</v>
-      </c>
-      <c r="N86" t="s">
-        <v>223</v>
-      </c>
-      <c r="T86" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
@@ -5551,22 +5551,22 @@
         <v>31</v>
       </c>
       <c r="C87" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D87" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E87">
         <v>85</v>
       </c>
       <c r="F87" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G87" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H87" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -5575,19 +5575,19 @@
         <v>5</v>
       </c>
       <c r="K87" t="s">
+        <v>218</v>
+      </c>
+      <c r="L87" t="s">
+        <v>219</v>
+      </c>
+      <c r="M87" t="s">
         <v>220</v>
       </c>
-      <c r="L87" t="s">
+      <c r="N87" t="s">
         <v>221</v>
       </c>
-      <c r="M87" t="s">
+      <c r="T87" t="s">
         <v>222</v>
-      </c>
-      <c r="N87" t="s">
-        <v>223</v>
-      </c>
-      <c r="T87" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
@@ -5595,22 +5595,22 @@
         <v>32</v>
       </c>
       <c r="C88" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D88" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E88">
         <v>86</v>
       </c>
       <c r="F88" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G88" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H88" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -5619,19 +5619,19 @@
         <v>5</v>
       </c>
       <c r="K88" t="s">
+        <v>218</v>
+      </c>
+      <c r="L88" t="s">
+        <v>219</v>
+      </c>
+      <c r="M88" t="s">
         <v>220</v>
       </c>
-      <c r="L88" t="s">
+      <c r="N88" t="s">
         <v>221</v>
       </c>
-      <c r="M88" t="s">
+      <c r="T88" t="s">
         <v>222</v>
-      </c>
-      <c r="N88" t="s">
-        <v>223</v>
-      </c>
-      <c r="T88" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
@@ -5639,22 +5639,22 @@
         <v>32</v>
       </c>
       <c r="C89" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D89" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E89">
         <v>87</v>
       </c>
       <c r="F89" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G89" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H89" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -5663,19 +5663,19 @@
         <v>5</v>
       </c>
       <c r="K89" t="s">
+        <v>218</v>
+      </c>
+      <c r="L89" t="s">
+        <v>219</v>
+      </c>
+      <c r="M89" t="s">
         <v>220</v>
       </c>
-      <c r="L89" t="s">
+      <c r="N89" t="s">
         <v>221</v>
       </c>
-      <c r="M89" t="s">
+      <c r="T89" t="s">
         <v>222</v>
-      </c>
-      <c r="N89" t="s">
-        <v>223</v>
-      </c>
-      <c r="T89" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
@@ -5683,22 +5683,22 @@
         <v>32</v>
       </c>
       <c r="C90" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D90" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E90">
         <v>88</v>
       </c>
       <c r="F90" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G90" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H90" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -5707,19 +5707,19 @@
         <v>5</v>
       </c>
       <c r="K90" t="s">
+        <v>218</v>
+      </c>
+      <c r="L90" t="s">
+        <v>219</v>
+      </c>
+      <c r="M90" t="s">
         <v>220</v>
       </c>
-      <c r="L90" t="s">
+      <c r="N90" t="s">
         <v>221</v>
       </c>
-      <c r="M90" t="s">
+      <c r="T90" t="s">
         <v>222</v>
-      </c>
-      <c r="N90" t="s">
-        <v>223</v>
-      </c>
-      <c r="T90" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
@@ -5727,22 +5727,22 @@
         <v>33</v>
       </c>
       <c r="C91" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D91" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E91">
         <v>89</v>
       </c>
       <c r="F91" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G91" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H91" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -5751,19 +5751,19 @@
         <v>5</v>
       </c>
       <c r="K91" t="s">
+        <v>218</v>
+      </c>
+      <c r="L91" t="s">
+        <v>219</v>
+      </c>
+      <c r="M91" t="s">
         <v>220</v>
       </c>
-      <c r="L91" t="s">
+      <c r="N91" t="s">
         <v>221</v>
       </c>
-      <c r="M91" t="s">
+      <c r="T91" t="s">
         <v>222</v>
-      </c>
-      <c r="N91" t="s">
-        <v>223</v>
-      </c>
-      <c r="T91" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
@@ -5771,22 +5771,22 @@
         <v>33</v>
       </c>
       <c r="C92" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D92" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E92">
         <v>90</v>
       </c>
       <c r="F92" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G92" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H92" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -5795,19 +5795,19 @@
         <v>5</v>
       </c>
       <c r="K92" t="s">
+        <v>218</v>
+      </c>
+      <c r="L92" t="s">
+        <v>219</v>
+      </c>
+      <c r="M92" t="s">
         <v>220</v>
       </c>
-      <c r="L92" t="s">
+      <c r="N92" t="s">
         <v>221</v>
       </c>
-      <c r="M92" t="s">
+      <c r="T92" t="s">
         <v>222</v>
-      </c>
-      <c r="N92" t="s">
-        <v>223</v>
-      </c>
-      <c r="T92" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
@@ -5815,22 +5815,22 @@
         <v>33</v>
       </c>
       <c r="C93" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D93" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E93">
         <v>91</v>
       </c>
       <c r="F93" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G93" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H93" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -5839,19 +5839,19 @@
         <v>5</v>
       </c>
       <c r="K93" t="s">
+        <v>218</v>
+      </c>
+      <c r="L93" t="s">
+        <v>219</v>
+      </c>
+      <c r="M93" t="s">
         <v>220</v>
       </c>
-      <c r="L93" t="s">
+      <c r="N93" t="s">
         <v>221</v>
       </c>
-      <c r="M93" t="s">
+      <c r="T93" t="s">
         <v>222</v>
-      </c>
-      <c r="N93" t="s">
-        <v>223</v>
-      </c>
-      <c r="T93" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
@@ -5859,22 +5859,22 @@
         <v>34</v>
       </c>
       <c r="C94" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D94" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E94">
         <v>92</v>
       </c>
       <c r="F94" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G94" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H94" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -5883,19 +5883,19 @@
         <v>5</v>
       </c>
       <c r="K94" t="s">
+        <v>218</v>
+      </c>
+      <c r="L94" t="s">
+        <v>219</v>
+      </c>
+      <c r="M94" t="s">
         <v>220</v>
       </c>
-      <c r="L94" t="s">
+      <c r="N94" t="s">
         <v>221</v>
       </c>
-      <c r="M94" t="s">
+      <c r="T94" t="s">
         <v>222</v>
-      </c>
-      <c r="N94" t="s">
-        <v>223</v>
-      </c>
-      <c r="T94" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
@@ -5903,22 +5903,22 @@
         <v>34</v>
       </c>
       <c r="C95" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D95" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E95">
         <v>93</v>
       </c>
       <c r="F95" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G95" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H95" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -5927,19 +5927,19 @@
         <v>5</v>
       </c>
       <c r="K95" t="s">
+        <v>218</v>
+      </c>
+      <c r="L95" t="s">
+        <v>219</v>
+      </c>
+      <c r="M95" t="s">
         <v>220</v>
       </c>
-      <c r="L95" t="s">
+      <c r="N95" t="s">
         <v>221</v>
       </c>
-      <c r="M95" t="s">
+      <c r="T95" t="s">
         <v>222</v>
-      </c>
-      <c r="N95" t="s">
-        <v>223</v>
-      </c>
-      <c r="T95" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.25">
@@ -5947,22 +5947,22 @@
         <v>34</v>
       </c>
       <c r="C96" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D96" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E96">
         <v>94</v>
       </c>
       <c r="F96" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G96" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H96" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -5971,19 +5971,19 @@
         <v>5</v>
       </c>
       <c r="K96" t="s">
+        <v>218</v>
+      </c>
+      <c r="L96" t="s">
+        <v>219</v>
+      </c>
+      <c r="M96" t="s">
         <v>220</v>
       </c>
-      <c r="L96" t="s">
+      <c r="N96" t="s">
         <v>221</v>
       </c>
-      <c r="M96" t="s">
+      <c r="T96" t="s">
         <v>222</v>
-      </c>
-      <c r="N96" t="s">
-        <v>223</v>
-      </c>
-      <c r="T96" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.25">
@@ -5991,22 +5991,22 @@
         <v>35</v>
       </c>
       <c r="C97" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D97" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E97">
         <v>95</v>
       </c>
       <c r="F97" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G97" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H97" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -6015,19 +6015,19 @@
         <v>5</v>
       </c>
       <c r="K97" t="s">
+        <v>218</v>
+      </c>
+      <c r="L97" t="s">
+        <v>219</v>
+      </c>
+      <c r="M97" t="s">
         <v>220</v>
       </c>
-      <c r="L97" t="s">
+      <c r="N97" t="s">
         <v>221</v>
       </c>
-      <c r="M97" t="s">
+      <c r="T97" t="s">
         <v>222</v>
-      </c>
-      <c r="N97" t="s">
-        <v>223</v>
-      </c>
-      <c r="T97" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.25">
@@ -6035,22 +6035,22 @@
         <v>35</v>
       </c>
       <c r="C98" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D98" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E98">
         <v>96</v>
       </c>
       <c r="F98" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G98" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H98" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -6059,19 +6059,19 @@
         <v>5</v>
       </c>
       <c r="K98" t="s">
+        <v>218</v>
+      </c>
+      <c r="L98" t="s">
+        <v>219</v>
+      </c>
+      <c r="M98" t="s">
         <v>220</v>
       </c>
-      <c r="L98" t="s">
+      <c r="N98" t="s">
         <v>221</v>
       </c>
-      <c r="M98" t="s">
+      <c r="T98" t="s">
         <v>222</v>
-      </c>
-      <c r="N98" t="s">
-        <v>223</v>
-      </c>
-      <c r="T98" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.25">
@@ -6079,22 +6079,22 @@
         <v>35</v>
       </c>
       <c r="C99" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D99" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E99">
         <v>97</v>
       </c>
       <c r="F99" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G99" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H99" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -6103,19 +6103,19 @@
         <v>5</v>
       </c>
       <c r="K99" t="s">
+        <v>218</v>
+      </c>
+      <c r="L99" t="s">
+        <v>219</v>
+      </c>
+      <c r="M99" t="s">
         <v>220</v>
       </c>
-      <c r="L99" t="s">
+      <c r="N99" t="s">
         <v>221</v>
       </c>
-      <c r="M99" t="s">
+      <c r="T99" t="s">
         <v>222</v>
-      </c>
-      <c r="N99" t="s">
-        <v>223</v>
-      </c>
-      <c r="T99" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.25">
@@ -6123,22 +6123,22 @@
         <v>36</v>
       </c>
       <c r="C100" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D100" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E100">
         <v>98</v>
       </c>
       <c r="F100" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G100" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H100" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -6147,19 +6147,19 @@
         <v>5</v>
       </c>
       <c r="K100" t="s">
+        <v>218</v>
+      </c>
+      <c r="L100" t="s">
+        <v>219</v>
+      </c>
+      <c r="M100" t="s">
         <v>220</v>
       </c>
-      <c r="L100" t="s">
+      <c r="N100" t="s">
         <v>221</v>
       </c>
-      <c r="M100" t="s">
+      <c r="T100" t="s">
         <v>222</v>
-      </c>
-      <c r="N100" t="s">
-        <v>223</v>
-      </c>
-      <c r="T100" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.25">
@@ -6167,22 +6167,22 @@
         <v>37</v>
       </c>
       <c r="C101" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D101" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E101">
         <v>99</v>
       </c>
       <c r="F101" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G101" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H101" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -6191,19 +6191,19 @@
         <v>6</v>
       </c>
       <c r="K101" t="s">
+        <v>299</v>
+      </c>
+      <c r="L101" t="s">
+        <v>300</v>
+      </c>
+      <c r="M101" t="s">
         <v>301</v>
       </c>
-      <c r="L101" t="s">
+      <c r="N101" t="s">
         <v>302</v>
       </c>
-      <c r="M101" t="s">
+      <c r="T101" t="s">
         <v>303</v>
-      </c>
-      <c r="N101" t="s">
-        <v>304</v>
-      </c>
-      <c r="T101" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.25">
@@ -6211,22 +6211,22 @@
         <v>37</v>
       </c>
       <c r="C102" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D102" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E102">
         <v>100</v>
       </c>
       <c r="F102" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G102" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H102" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -6235,19 +6235,19 @@
         <v>6</v>
       </c>
       <c r="K102" t="s">
+        <v>299</v>
+      </c>
+      <c r="L102" t="s">
+        <v>300</v>
+      </c>
+      <c r="M102" t="s">
         <v>301</v>
       </c>
-      <c r="L102" t="s">
+      <c r="N102" t="s">
         <v>302</v>
       </c>
-      <c r="M102" t="s">
+      <c r="T102" t="s">
         <v>303</v>
-      </c>
-      <c r="N102" t="s">
-        <v>304</v>
-      </c>
-      <c r="T102" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.25">
@@ -6255,25 +6255,25 @@
         <v>38</v>
       </c>
       <c r="C103" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D103" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E103">
         <v>101</v>
       </c>
       <c r="F103" t="s">
+        <v>307</v>
+      </c>
+      <c r="G103" t="s">
+        <v>308</v>
+      </c>
+      <c r="H103" t="s">
         <v>309</v>
       </c>
-      <c r="G103" t="s">
+      <c r="T103" t="s">
         <v>310</v>
-      </c>
-      <c r="H103" t="s">
-        <v>311</v>
-      </c>
-      <c r="T103" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.25">
@@ -6281,34 +6281,34 @@
         <v>38</v>
       </c>
       <c r="C104" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D104" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E104">
         <v>102</v>
       </c>
       <c r="F104" t="s">
+        <v>311</v>
+      </c>
+      <c r="G104" t="s">
+        <v>312</v>
+      </c>
+      <c r="H104" t="s">
         <v>313</v>
       </c>
-      <c r="G104" t="s">
+      <c r="Q104" t="s">
         <v>314</v>
       </c>
-      <c r="H104" t="s">
+      <c r="R104" t="s">
         <v>315</v>
       </c>
-      <c r="Q104" t="s">
+      <c r="S104" t="s">
         <v>316</v>
       </c>
-      <c r="R104" t="s">
-        <v>317</v>
-      </c>
-      <c r="S104" t="s">
-        <v>318</v>
-      </c>
       <c r="T104" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.25">
@@ -6316,22 +6316,22 @@
         <v>39</v>
       </c>
       <c r="C105" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D105" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E105">
         <v>103</v>
       </c>
       <c r="F105" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H105" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -6340,19 +6340,19 @@
         <v>10</v>
       </c>
       <c r="K105" t="s">
+        <v>319</v>
+      </c>
+      <c r="L105" t="s">
+        <v>320</v>
+      </c>
+      <c r="M105" t="s">
         <v>321</v>
       </c>
-      <c r="L105" t="s">
+      <c r="N105" t="s">
         <v>322</v>
       </c>
-      <c r="M105" t="s">
-        <v>323</v>
-      </c>
-      <c r="N105" t="s">
-        <v>324</v>
-      </c>
       <c r="T105" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.25">
@@ -6360,22 +6360,22 @@
         <v>39</v>
       </c>
       <c r="C106" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D106" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E106">
         <v>104</v>
       </c>
       <c r="F106" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G106" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H106" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -6384,19 +6384,19 @@
         <v>10</v>
       </c>
       <c r="K106" t="s">
+        <v>319</v>
+      </c>
+      <c r="L106" t="s">
+        <v>320</v>
+      </c>
+      <c r="M106" t="s">
         <v>321</v>
       </c>
-      <c r="L106" t="s">
+      <c r="N106" t="s">
         <v>322</v>
       </c>
-      <c r="M106" t="s">
-        <v>323</v>
-      </c>
-      <c r="N106" t="s">
-        <v>324</v>
-      </c>
       <c r="T106" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.25">
@@ -6404,22 +6404,22 @@
         <v>39</v>
       </c>
       <c r="C107" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D107" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E107">
         <v>105</v>
       </c>
       <c r="F107" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G107" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H107" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -6428,19 +6428,19 @@
         <v>10</v>
       </c>
       <c r="K107" t="s">
+        <v>319</v>
+      </c>
+      <c r="L107" t="s">
+        <v>320</v>
+      </c>
+      <c r="M107" t="s">
         <v>321</v>
       </c>
-      <c r="L107" t="s">
+      <c r="N107" t="s">
         <v>322</v>
       </c>
-      <c r="M107" t="s">
-        <v>323</v>
-      </c>
-      <c r="N107" t="s">
-        <v>324</v>
-      </c>
       <c r="T107" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.25">
@@ -6448,22 +6448,22 @@
         <v>40</v>
       </c>
       <c r="C108" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D108" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E108">
         <v>106</v>
       </c>
       <c r="F108" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G108" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H108" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -6472,19 +6472,19 @@
         <v>10</v>
       </c>
       <c r="K108" t="s">
+        <v>319</v>
+      </c>
+      <c r="L108" t="s">
+        <v>320</v>
+      </c>
+      <c r="M108" t="s">
         <v>321</v>
       </c>
-      <c r="L108" t="s">
+      <c r="N108" t="s">
         <v>322</v>
       </c>
-      <c r="M108" t="s">
-        <v>323</v>
-      </c>
-      <c r="N108" t="s">
-        <v>324</v>
-      </c>
       <c r="T108" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.25">
@@ -6492,25 +6492,25 @@
         <v>40</v>
       </c>
       <c r="C109" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D109" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E109">
         <v>107</v>
       </c>
       <c r="F109" t="s">
+        <v>329</v>
+      </c>
+      <c r="G109" t="s">
+        <v>330</v>
+      </c>
+      <c r="H109" t="s">
         <v>331</v>
       </c>
-      <c r="G109" t="s">
-        <v>332</v>
-      </c>
-      <c r="H109" t="s">
-        <v>333</v>
-      </c>
       <c r="T109" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.25">
@@ -6518,22 +6518,22 @@
         <v>40</v>
       </c>
       <c r="C110" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D110" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E110">
         <v>108</v>
       </c>
       <c r="F110" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G110" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H110" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I110" s="1">
         <v>0</v>
@@ -6542,19 +6542,19 @@
         <v>1</v>
       </c>
       <c r="K110" t="s">
+        <v>334</v>
+      </c>
+      <c r="L110" t="s">
+        <v>335</v>
+      </c>
+      <c r="M110" t="s">
         <v>336</v>
       </c>
-      <c r="L110" t="s">
+      <c r="N110" t="s">
         <v>337</v>
       </c>
-      <c r="M110" t="s">
-        <v>338</v>
-      </c>
-      <c r="N110" t="s">
-        <v>339</v>
-      </c>
       <c r="T110" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.25">
@@ -6562,22 +6562,22 @@
         <v>41</v>
       </c>
       <c r="C111" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D111" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E111">
         <v>109</v>
       </c>
       <c r="F111" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G111" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H111" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -6586,19 +6586,19 @@
         <v>10</v>
       </c>
       <c r="K111" t="s">
+        <v>340</v>
+      </c>
+      <c r="L111" t="s">
+        <v>341</v>
+      </c>
+      <c r="M111" t="s">
         <v>342</v>
       </c>
-      <c r="L111" t="s">
+      <c r="N111" t="s">
         <v>343</v>
       </c>
-      <c r="M111" t="s">
-        <v>344</v>
-      </c>
-      <c r="N111" t="s">
-        <v>345</v>
-      </c>
       <c r="T111" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.25">
@@ -6606,22 +6606,22 @@
         <v>41</v>
       </c>
       <c r="C112" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D112" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E112">
         <v>110</v>
       </c>
       <c r="F112" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G112" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H112" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -6630,19 +6630,19 @@
         <v>10</v>
       </c>
       <c r="K112" t="s">
+        <v>340</v>
+      </c>
+      <c r="L112" t="s">
+        <v>341</v>
+      </c>
+      <c r="M112" t="s">
         <v>342</v>
       </c>
-      <c r="L112" t="s">
+      <c r="N112" t="s">
         <v>343</v>
       </c>
-      <c r="M112" t="s">
-        <v>344</v>
-      </c>
-      <c r="N112" t="s">
-        <v>345</v>
-      </c>
       <c r="T112" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.25">
@@ -6650,22 +6650,22 @@
         <v>41</v>
       </c>
       <c r="C113" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D113" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E113">
         <v>111</v>
       </c>
       <c r="F113" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G113" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H113" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -6674,19 +6674,19 @@
         <v>10</v>
       </c>
       <c r="K113" t="s">
+        <v>340</v>
+      </c>
+      <c r="L113" t="s">
+        <v>341</v>
+      </c>
+      <c r="M113" t="s">
         <v>342</v>
       </c>
-      <c r="L113" t="s">
+      <c r="N113" t="s">
         <v>343</v>
       </c>
-      <c r="M113" t="s">
-        <v>344</v>
-      </c>
-      <c r="N113" t="s">
-        <v>345</v>
-      </c>
       <c r="T113" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.25">
@@ -6694,22 +6694,22 @@
         <v>42</v>
       </c>
       <c r="C114" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D114" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E114">
         <v>112</v>
       </c>
       <c r="F114" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G114" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H114" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -6718,19 +6718,19 @@
         <v>10</v>
       </c>
       <c r="K114" t="s">
+        <v>340</v>
+      </c>
+      <c r="L114" t="s">
+        <v>341</v>
+      </c>
+      <c r="M114" t="s">
         <v>342</v>
       </c>
-      <c r="L114" t="s">
+      <c r="N114" t="s">
         <v>343</v>
       </c>
-      <c r="M114" t="s">
-        <v>344</v>
-      </c>
-      <c r="N114" t="s">
-        <v>345</v>
-      </c>
       <c r="T114" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.25">
@@ -6738,22 +6738,22 @@
         <v>42</v>
       </c>
       <c r="C115" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D115" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E115">
         <v>113</v>
       </c>
       <c r="F115" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G115" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H115" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -6762,19 +6762,19 @@
         <v>10</v>
       </c>
       <c r="K115" t="s">
+        <v>340</v>
+      </c>
+      <c r="L115" t="s">
+        <v>341</v>
+      </c>
+      <c r="M115" t="s">
         <v>342</v>
       </c>
-      <c r="L115" t="s">
+      <c r="N115" t="s">
         <v>343</v>
       </c>
-      <c r="M115" t="s">
-        <v>344</v>
-      </c>
-      <c r="N115" t="s">
-        <v>345</v>
-      </c>
       <c r="T115" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.25">
@@ -6782,22 +6782,22 @@
         <v>42</v>
       </c>
       <c r="C116" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D116" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E116">
         <v>114</v>
       </c>
       <c r="F116" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G116" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H116" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -6806,19 +6806,19 @@
         <v>10</v>
       </c>
       <c r="K116" t="s">
+        <v>340</v>
+      </c>
+      <c r="L116" t="s">
+        <v>341</v>
+      </c>
+      <c r="M116" t="s">
         <v>342</v>
       </c>
-      <c r="L116" t="s">
+      <c r="N116" t="s">
         <v>343</v>
       </c>
-      <c r="M116" t="s">
-        <v>344</v>
-      </c>
-      <c r="N116" t="s">
-        <v>345</v>
-      </c>
       <c r="T116" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="117" spans="1:20" x14ac:dyDescent="0.25">
@@ -6826,22 +6826,22 @@
         <v>43</v>
       </c>
       <c r="C117" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D117" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E117">
         <v>115</v>
       </c>
       <c r="F117" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G117" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H117" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -6850,19 +6850,19 @@
         <v>10</v>
       </c>
       <c r="K117" t="s">
+        <v>340</v>
+      </c>
+      <c r="L117" t="s">
+        <v>341</v>
+      </c>
+      <c r="M117" t="s">
         <v>342</v>
       </c>
-      <c r="L117" t="s">
+      <c r="N117" t="s">
         <v>343</v>
       </c>
-      <c r="M117" t="s">
-        <v>344</v>
-      </c>
-      <c r="N117" t="s">
-        <v>345</v>
-      </c>
       <c r="T117" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
